--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\《梦境之旅》Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitDreamJourney\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC028A3-03BF-4824-A66B-6AEDE6F8660C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9381C5B5-E283-4AAE-8ECD-9DC0FF11B547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1134,7 +1134,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="2">
-        <v>1000102</v>
+        <v>1000101</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
@@ -1165,7 +1165,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="2">
-        <v>1000103</v>
+        <v>1000101</v>
       </c>
       <c r="F13" s="2">
         <v>5</v>
@@ -1196,7 +1196,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="2">
-        <v>1000104</v>
+        <v>1000101</v>
       </c>
       <c r="F14" s="2">
         <v>5</v>
@@ -1227,7 +1227,7 @@
         <v>29</v>
       </c>
       <c r="E15" s="2">
-        <v>1000105</v>
+        <v>1000101</v>
       </c>
       <c r="F15" s="2">
         <v>5</v>
@@ -1258,7 +1258,7 @@
         <v>31</v>
       </c>
       <c r="E16" s="2">
-        <v>1000106</v>
+        <v>1000101</v>
       </c>
       <c r="F16" s="2">
         <v>5</v>
@@ -1289,7 +1289,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="2">
-        <v>1000107</v>
+        <v>1000101</v>
       </c>
       <c r="F17" s="2">
         <v>5</v>
@@ -1320,7 +1320,7 @@
         <v>35</v>
       </c>
       <c r="E18" s="2">
-        <v>1000108</v>
+        <v>1000101</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
@@ -1351,7 +1351,7 @@
         <v>37</v>
       </c>
       <c r="E19" s="2">
-        <v>1000109</v>
+        <v>1000101</v>
       </c>
       <c r="F19" s="2">
         <v>5</v>
@@ -1382,7 +1382,7 @@
         <v>39</v>
       </c>
       <c r="E20" s="2">
-        <v>1000110</v>
+        <v>1000101</v>
       </c>
       <c r="F20" s="2">
         <v>3</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitDreamJourney\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9381C5B5-E283-4AAE-8ECD-9DC0FF11B547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -41,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -54,14 +59,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -70,25 +74,23 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 1.消耗型道具
 2.材料
 3.装备
-4.技能碎片</t>
+4.英雄碎片</t>
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -97,7 +99,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -108,7 +109,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="微软雅黑"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">当道具类型为1（消耗品）时字段的意义
@@ -127,7 +127,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="微软雅黑"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>当道具类型为3（装备）时该字段的意义
@@ -150,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>Id</t>
   </si>
@@ -179,6 +178,30 @@
     <t>道具描述</t>
   </si>
   <si>
+    <t>ItemName</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>ItemSubType</t>
+  </si>
+  <si>
+    <t>ItemPileSum</t>
+  </si>
+  <si>
+    <t>ItemEquipID</t>
+  </si>
+  <si>
+    <t>ItemDescription</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -275,34 +298,10 @@
     <t>消耗入场券进入副本</t>
   </si>
   <si>
-    <t>绿色品质技能</t>
-  </si>
-  <si>
-    <t>这是一个绿色品质的技能，释放后造成32%的伤害</t>
-  </si>
-  <si>
-    <t>蓝色品质技能</t>
-  </si>
-  <si>
-    <t>这是一个蓝色品质的技能，释放后造成64%的伤害</t>
-  </si>
-  <si>
-    <t>紫色品质技能</t>
-  </si>
-  <si>
-    <t>这是一个紫色品质的技能，释放后造成96%的伤害</t>
-  </si>
-  <si>
-    <t>橙色品质技能</t>
-  </si>
-  <si>
-    <t>这是一个橙色品质的技能，释放后造成128%的伤害</t>
-  </si>
-  <si>
-    <t>红色品质技能</t>
-  </si>
-  <si>
-    <t>这是一个红色品质的技能，释放后造成160%的伤害</t>
+    <t>大熊猫碎片</t>
+  </si>
+  <si>
+    <t>英雄碎片，八个合成</t>
   </si>
   <si>
     <t>一个头盔</t>
@@ -336,49 +335,19 @@
   </si>
   <si>
     <t>一个武器</t>
-  </si>
-  <si>
-    <t>ItemName</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemQuality</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemSubType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemPileSum</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemEquipID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemDescription</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,7 +359,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -398,59 +366,189 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,19 +557,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505021"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14996795556505"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,8 +585,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -539,12 +823,254 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -568,25 +1094,69 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -844,14 +1414,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.875" style="5" customWidth="1"/>
     <col min="3" max="10" width="17.875" style="5"/>
@@ -859,9 +1429,9 @@
     <col min="12" max="16384" width="17.875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1"/>
+    <row r="2" s="1" customFormat="1" customHeight="1"/>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
@@ -890,70 +1460,70 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C4" s="6" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C5" s="6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:11">
       <c r="C6" s="5">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E6" s="5">
         <v>1</v>
@@ -974,15 +1544,15 @@
         <v>0</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:11">
       <c r="C7" s="5">
         <v>2</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -1003,15 +1573,15 @@
         <v>0</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:11">
       <c r="C8" s="5">
         <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5">
         <v>3</v>
@@ -1032,15 +1602,15 @@
         <v>0</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:11">
       <c r="C9" s="5">
         <v>4</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5">
         <v>4</v>
@@ -1061,15 +1631,15 @@
         <v>0</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:11">
       <c r="C10" s="5">
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E10" s="5">
         <v>5</v>
@@ -1090,17 +1660,17 @@
         <v>0</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="2">
         <v>10000101</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2">
         <v>1000101</v>
@@ -1121,17 +1691,17 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:11">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="2">
         <v>10000102</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2">
         <v>1000101</v>
@@ -1152,17 +1722,17 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="2">
         <v>10000103</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2">
         <v>1000101</v>
@@ -1183,17 +1753,17 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="2">
         <v>10000104</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2">
         <v>1000101</v>
@@ -1214,17 +1784,17 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="2">
         <v>10000105</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2">
         <v>1000101</v>
@@ -1245,17 +1815,17 @@
         <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="2">
         <v>10000106</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2">
         <v>1000101</v>
@@ -1276,17 +1846,17 @@
         <v>0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="2">
         <v>10000107</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2">
         <v>1000101</v>
@@ -1307,17 +1877,17 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="2">
         <v>10000108</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2">
         <v>1000101</v>
@@ -1338,17 +1908,17 @@
         <v>0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="2">
         <v>10000109</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2">
         <v>1000101</v>
@@ -1369,17 +1939,17 @@
         <v>0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="2">
         <v>10000110</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E20" s="2">
         <v>1000101</v>
@@ -1400,17 +1970,17 @@
         <v>0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="3">
         <v>11000001</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E21" s="3">
         <v>11000001</v>
@@ -1431,17 +2001,17 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="3">
         <v>11000002</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E22" s="3">
         <v>11000002</v>
@@ -1462,17 +2032,17 @@
         <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="3">
         <v>11000003</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3">
         <v>11000003</v>
@@ -1493,17 +2063,17 @@
         <v>0</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="3">
         <v>11000004</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3">
         <v>11000004</v>
@@ -1524,10 +2094,10 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="3">
@@ -1558,7 +2128,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="4">
@@ -1586,7 +2156,7 @@
         <v>12000001</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="4">
@@ -1614,7 +2184,7 @@
         <v>12000002</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="4">
@@ -1642,7 +2212,7 @@
         <v>12000003</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="4">
@@ -1670,7 +2240,7 @@
         <v>12000004</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="4">
@@ -1698,7 +2268,7 @@
         <v>12000005</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="4">
@@ -1726,7 +2296,7 @@
         <v>12000006</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="4">
@@ -1754,7 +2324,7 @@
         <v>12000007</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4">
@@ -1782,7 +2352,7 @@
         <v>12000008</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="4">
@@ -1810,7 +2380,7 @@
         <v>12000009</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="4">
@@ -1838,7 +2408,7 @@
         <v>12000010</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="4">
@@ -1867,8 +2437,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -32,6 +32,28 @@
     <author>admin</author>
   </authors>
   <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+资源位置在Assets\Bundles\Icon\ItemIcon</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F3" authorId="0">
       <text>
         <r>
@@ -144,6 +166,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="J3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表EquipConfig</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -347,7 +391,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,24 +563,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
@@ -548,7 +585,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,12 +745,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1040,37 +1071,37 @@
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1673,7 +1704,7 @@
         <v>29</v>
       </c>
       <c r="E11" s="2">
-        <v>1000101</v>
+        <v>10000001</v>
       </c>
       <c r="F11" s="2">
         <v>6</v>
@@ -1704,7 +1735,7 @@
         <v>31</v>
       </c>
       <c r="E12" s="2">
-        <v>1000101</v>
+        <v>10000002</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
@@ -1735,7 +1766,7 @@
         <v>33</v>
       </c>
       <c r="E13" s="2">
-        <v>1000101</v>
+        <v>10000003</v>
       </c>
       <c r="F13" s="2">
         <v>5</v>
@@ -1766,7 +1797,7 @@
         <v>35</v>
       </c>
       <c r="E14" s="2">
-        <v>1000101</v>
+        <v>10000004</v>
       </c>
       <c r="F14" s="2">
         <v>5</v>
@@ -1797,7 +1828,7 @@
         <v>37</v>
       </c>
       <c r="E15" s="2">
-        <v>1000101</v>
+        <v>10000005</v>
       </c>
       <c r="F15" s="2">
         <v>5</v>
@@ -1828,7 +1859,7 @@
         <v>39</v>
       </c>
       <c r="E16" s="2">
-        <v>1000101</v>
+        <v>10000006</v>
       </c>
       <c r="F16" s="2">
         <v>5</v>
@@ -1859,7 +1890,7 @@
         <v>41</v>
       </c>
       <c r="E17" s="2">
-        <v>1000101</v>
+        <v>10000007</v>
       </c>
       <c r="F17" s="2">
         <v>5</v>
@@ -1890,7 +1921,7 @@
         <v>43</v>
       </c>
       <c r="E18" s="2">
-        <v>1000101</v>
+        <v>10000008</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
@@ -1921,7 +1952,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="2">
-        <v>1000101</v>
+        <v>10000009</v>
       </c>
       <c r="F19" s="2">
         <v>5</v>
@@ -1952,7 +1983,7 @@
         <v>47</v>
       </c>
       <c r="E20" s="2">
-        <v>1000101</v>
+        <v>10000010</v>
       </c>
       <c r="F20" s="2">
         <v>3</v>
@@ -1983,7 +2014,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="3">
-        <v>11000001</v>
+        <v>10000011</v>
       </c>
       <c r="F21" s="3">
         <v>2</v>
@@ -2014,7 +2045,7 @@
         <v>49</v>
       </c>
       <c r="E22" s="3">
-        <v>11000002</v>
+        <v>10000012</v>
       </c>
       <c r="F22" s="3">
         <v>3</v>
@@ -2045,7 +2076,7 @@
         <v>49</v>
       </c>
       <c r="E23" s="3">
-        <v>11000003</v>
+        <v>10000013</v>
       </c>
       <c r="F23" s="3">
         <v>4</v>
@@ -2076,7 +2107,7 @@
         <v>49</v>
       </c>
       <c r="E24" s="3">
-        <v>11000004</v>
+        <v>10000014</v>
       </c>
       <c r="F24" s="3">
         <v>5</v>
@@ -2107,7 +2138,7 @@
         <v>49</v>
       </c>
       <c r="E25" s="3">
-        <v>11000005</v>
+        <v>10000015</v>
       </c>
       <c r="F25" s="3">
         <v>6</v>
@@ -2138,7 +2169,7 @@
         <v>51</v>
       </c>
       <c r="E26" s="4">
-        <v>12000001</v>
+        <v>10000001</v>
       </c>
       <c r="F26" s="4">
         <v>3</v>
@@ -2166,7 +2197,7 @@
         <v>52</v>
       </c>
       <c r="E27" s="4">
-        <v>12000002</v>
+        <v>10000002</v>
       </c>
       <c r="F27" s="4">
         <v>3</v>
@@ -2194,7 +2225,7 @@
         <v>53</v>
       </c>
       <c r="E28" s="4">
-        <v>12000003</v>
+        <v>10000003</v>
       </c>
       <c r="F28" s="4">
         <v>3</v>
@@ -2222,7 +2253,7 @@
         <v>54</v>
       </c>
       <c r="E29" s="4">
-        <v>12000004</v>
+        <v>10000004</v>
       </c>
       <c r="F29" s="4">
         <v>3</v>
@@ -2250,7 +2281,7 @@
         <v>55</v>
       </c>
       <c r="E30" s="4">
-        <v>12000005</v>
+        <v>10000005</v>
       </c>
       <c r="F30" s="4">
         <v>3</v>
@@ -2278,7 +2309,7 @@
         <v>56</v>
       </c>
       <c r="E31" s="4">
-        <v>12000006</v>
+        <v>10000006</v>
       </c>
       <c r="F31" s="4">
         <v>3</v>
@@ -2306,7 +2337,7 @@
         <v>57</v>
       </c>
       <c r="E32" s="4">
-        <v>12000007</v>
+        <v>10000007</v>
       </c>
       <c r="F32" s="4">
         <v>3</v>
@@ -2334,7 +2365,7 @@
         <v>58</v>
       </c>
       <c r="E33" s="4">
-        <v>12000008</v>
+        <v>10000008</v>
       </c>
       <c r="F33" s="4">
         <v>3</v>
@@ -2362,7 +2393,7 @@
         <v>59</v>
       </c>
       <c r="E34" s="4">
-        <v>12000009</v>
+        <v>10000009</v>
       </c>
       <c r="F34" s="4">
         <v>3</v>
@@ -2390,7 +2421,7 @@
         <v>60</v>
       </c>
       <c r="E35" s="4">
-        <v>12000010</v>
+        <v>10000010</v>
       </c>
       <c r="F35" s="4">
         <v>3</v>
@@ -2418,7 +2449,7 @@
         <v>61</v>
       </c>
       <c r="E36" s="4">
-        <v>12000011</v>
+        <v>10000011</v>
       </c>
       <c r="F36" s="4">
         <v>3</v>
